--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6610169491525424</v>
+        <v>0.6554621848739496</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6338028169014085</v>
+        <v>0.6197183098591549</v>
       </c>
       <c r="D2">
-        <v>0.4</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="E2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
